--- a/data/canary/valcan_pack_2026-04-12/_VALCAN_2026/20_LOGISTICS/valcanary_po_register_2024.xlsx
+++ b/data/canary/valcan_pack_2026-04-12/_VALCAN_2026/20_LOGISTICS/valcanary_po_register_2024.xlsx
@@ -596,7 +596,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VALPO-9000000001</t>
+          <t>PO 9001000001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VALSITE-ALPHA</t>
+          <t>Site: Validation Alpha Site</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>VALPART-RG213-001</t>
+          <t>QZ-3001</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -634,7 +634,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VALPO-9000000002</t>
+          <t>PO 9001000002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VALSITE-BRAVO</t>
+          <t>Site: Validation Bravo Site</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>VALPART-UPS48V-003</t>
+          <t>QZ-3003</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -672,7 +672,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VALPO-9000000003</t>
+          <t>PO 9001000003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VALSITE-ALPHA</t>
+          <t>Site: Validation Alpha Site</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>VALPART-FAN-006</t>
+          <t>QZ-3006</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -710,7 +710,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VALPO-9000000004</t>
+          <t>PO 9001000004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VALSITE-CHARLIE</t>
+          <t>Site: Validation Charlie Site</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>VALPART-GPSANT-004</t>
+          <t>QZ-3004</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -748,7 +748,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VALPO-9000000005</t>
+          <t>PO 9001000005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VALSITE-DELTA</t>
+          <t>Site: Validation Delta Site</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>VALPART-CBL-010</t>
+          <t>QZ-3010</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -786,7 +786,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VALPO-9000000006</t>
+          <t>PO 9001000006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VALSITE-ECHO</t>
+          <t>Site: Validation Echo Site</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>VALPART-ROUTER-016</t>
+          <t>QZ-3016</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -824,7 +824,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VALPO-9000000007</t>
+          <t>PO 9001000007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VALSITE-BRAVO</t>
+          <t>Site: Validation Bravo Site</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>VALPART-SFP-014</t>
+          <t>QZ-3014</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -862,7 +862,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VALPO-9000000008</t>
+          <t>PO 9001000008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VALSITE-CHARLIE</t>
+          <t>Site: Validation Charlie Site</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>VALPART-UPSCARD-015</t>
+          <t>QZ-3015</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -900,7 +900,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VALPO-9000000009</t>
+          <t>PO 9001000009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VALSITE-ALPHA</t>
+          <t>Site: Validation Alpha Site</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>VALPART-NIC-013</t>
+          <t>QZ-3013</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -938,7 +938,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VALPO-9000000010</t>
+          <t>PO 9001000010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>VALSITE-ECHO</t>
+          <t>Site: Validation Echo Site</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>VALPART-PSU-008</t>
+          <t>QZ-3008</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -976,7 +976,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VALPO-9000000011</t>
+          <t>PO 9001000011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>VALSITE-DELTA</t>
+          <t>Site: Validation Delta Site</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>VALPART-BATT-007</t>
+          <t>QZ-3007</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1014,7 +1014,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VALPO-9000000012</t>
+          <t>PO 9001000012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VALSITE-CHARLIE</t>
+          <t>Site: Validation Charlie Site</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>VALPART-FLT-009</t>
+          <t>QZ-3009</t>
         </is>
       </c>
       <c r="H13" t="n">
